--- a/output/2021/sector_totals_v2.5_year2021.xlsx
+++ b/output/2021/sector_totals_v2.5_year2021.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1831.190748525657</v>
+        <v>1890.265436609341</v>
       </c>
       <c r="C3" t="n">
-        <v>123.8582088089857</v>
+        <v>114.1641217142191</v>
       </c>
       <c r="D3" t="n">
-        <v>728.6052854734597</v>
+        <v>747.3807002321477</v>
       </c>
       <c r="E3" t="n">
-        <v>2302.5387242886</v>
+        <v>2167.913296229455</v>
       </c>
       <c r="F3" t="n">
-        <v>197.7559639210259</v>
+        <v>191.7660700429966</v>
       </c>
       <c r="G3" t="n">
-        <v>91.84178589427546</v>
+        <v>85.00596112206401</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6228.308206974401</v>
+        <v>6287.382895058085</v>
       </c>
       <c r="C16" t="n">
-        <v>1011.824628534506</v>
+        <v>1002.13054143974</v>
       </c>
       <c r="D16" t="n">
-        <v>4906.446015535814</v>
+        <v>4925.221430294502</v>
       </c>
       <c r="E16" t="n">
-        <v>8960.152852360985</v>
+        <v>8825.527424301839</v>
       </c>
       <c r="F16" t="n">
-        <v>1686.802650135905</v>
+        <v>1680.812756257875</v>
       </c>
       <c r="G16" t="n">
-        <v>123.7840869447542</v>
+        <v>116.9482621725427</v>
       </c>
     </row>
   </sheetData>
